--- a/Luban/Config/Datas/AudioData.xlsx
+++ b/Luban/Config/Datas/AudioData.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1069,6 +1069,70 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>17</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>选关BGM</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>bgm_select</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>选关界面循环</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>18</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>战斗BGM</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>bgm_battle</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>战斗循环</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Luban/Config/Datas/AudioData.xlsx
+++ b/Luban/Config/Datas/AudioData.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -655,23 +655,23 @@
     </row>
     <row r="7">
       <c r="B7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>穿透塔开火</t>
+          <t>怪物受击</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>sfx_tower_fire_pierce</t>
+          <t>sfx_enemy_hit</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.5</v>
+        <v>0.35</v>
       </c>
       <c r="F7" t="n">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -681,29 +681,29 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>穿透塔开火，偏清脆</t>
+          <t>命中非致命</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>激光塔开火</t>
+          <t>怪物死亡</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>sfx_tower_fire_laser</t>
+          <t>sfx_enemy_death</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -713,26 +713,26 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>激光 hitscan</t>
+          <t>击杀</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>怪物受击</t>
+          <t>建造防御塔</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>sfx_enemy_hit</t>
+          <t>sfx_tower_build</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.35</v>
+        <v>0.7</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
@@ -745,29 +745,29 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>命中非致命</t>
+          <t>建塔成功</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>怪物死亡</t>
+          <t>升级防御塔</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>sfx_enemy_death</t>
+          <t>sfx_tower_upgrade</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -777,29 +777,29 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>击杀</t>
+          <t>升级成功</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>建造防御塔</t>
+          <t>出售防御塔</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>sfx_tower_build</t>
+          <t>sfx_tower_sell</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -809,29 +809,29 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>建塔成功</t>
+          <t>出售返还</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>升级防御塔</t>
+          <t>回合开始</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>sfx_tower_upgrade</t>
+          <t>sfx_round_start</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F12" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -841,29 +841,29 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>升级成功</t>
+          <t>回合开始</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>出售防御塔</t>
+          <t>回合完成</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>sfx_tower_sell</t>
+          <t>sfx_round_clear</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F13" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -873,29 +873,29 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>出售返还</t>
+          <t>回合清空</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>回合开始</t>
+          <t>漏怪</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>sfx_round_start</t>
+          <t>sfx_enemy_leak</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -905,26 +905,26 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>回合开始</t>
+          <t>怪物走到终点，负面反馈</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>回合完成</t>
+          <t>通关</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>sfx_round_clear</t>
+          <t>sfx_victory</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
@@ -937,30 +937,30 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>回合清空</t>
+          <t>全部回合完成</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>漏怪</t>
+          <t>失败</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>sfx_enemy_leak</t>
+          <t>sfx_defeat</t>
         </is>
       </c>
       <c r="E16" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F16" t="n">
         <v>0.85</v>
       </c>
-      <c r="F16" t="n">
-        <v>0.9</v>
-      </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
@@ -969,26 +969,26 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>怪物走到终点，负面反馈</t>
+          <t>生命归零</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>通关</t>
+          <t>按钮点击</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>sfx_victory</t>
+          <t>sfx_ui_click</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
@@ -1001,54 +1001,54 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>全部回合完成</t>
+          <t>通用 UI 点击</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>失败</t>
+          <t>选关BGM</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>sfx_defeat</t>
+          <t>bgm_select</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="F18" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>生命归零</t>
+          <t>选关界面循环</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>按钮点击</t>
+          <t>战斗BGM</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>sfx_ui_click</t>
+          <t>bgm_battle</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1058,76 +1058,12 @@
         <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
-        <is>
-          <t>通用 UI 点击</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" t="n">
-        <v>17</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>选关BGM</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>bgm_select</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>选关界面循环</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" t="n">
-        <v>18</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>战斗BGM</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>bgm_battle</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="inlineStr">
         <is>
           <t>战斗循环</t>
         </is>
